--- a/data.mn/public/datasets/meat-production-historical-total.xlsx
+++ b/data.mn/public/datasets/meat-production-historical-total.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,362 +422,602 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>production_thousand_tonnes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1940</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1940</v>
       </c>
       <c r="B2" t="n">
         <v>111</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1950</v>
       </c>
       <c r="B3" t="n">
         <v>157.3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1960</v>
       </c>
       <c r="B4" t="n">
         <v>184.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1961</v>
       </c>
       <c r="B5" t="n">
         <v>186.1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
+      <c r="A6" t="n">
+        <v>1962</v>
       </c>
       <c r="B6" t="n">
         <v>168.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
+      <c r="A7" t="n">
+        <v>1963</v>
       </c>
       <c r="B7" t="n">
         <v>146.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
+      <c r="A8" t="n">
+        <v>1964</v>
       </c>
       <c r="B8" t="n">
         <v>141.6</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
+      <c r="A9" t="n">
+        <v>1965</v>
       </c>
       <c r="B9" t="n">
         <v>169</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
+      <c r="A10" t="n">
+        <v>1966</v>
       </c>
       <c r="B10" t="n">
         <v>171.1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1967</t>
-        </is>
+      <c r="A11" t="n">
+        <v>1967</v>
       </c>
       <c r="B11" t="n">
         <v>183.1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
+      <c r="A12" t="n">
+        <v>1968</v>
       </c>
       <c r="B12" t="n">
         <v>163.3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
+      <c r="A13" t="n">
+        <v>1969</v>
       </c>
       <c r="B13" t="n">
         <v>180.7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
+      <c r="A14" t="n">
+        <v>1970</v>
       </c>
       <c r="B14" t="n">
         <v>179.8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
+      <c r="A15" t="n">
+        <v>1971</v>
       </c>
       <c r="B15" t="n">
         <v>176.1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
+      <c r="A16" t="n">
+        <v>1972</v>
       </c>
       <c r="B16" t="n">
         <v>197.8</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
+      <c r="A17" t="n">
+        <v>1973</v>
       </c>
       <c r="B17" t="n">
         <v>188.9</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
+      <c r="A18" t="n">
+        <v>1974</v>
       </c>
       <c r="B18" t="n">
         <v>215.5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
+      <c r="A19" t="n">
+        <v>1975</v>
       </c>
       <c r="B19" t="n">
         <v>234.6</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
+      <c r="A20" t="n">
+        <v>1976</v>
       </c>
       <c r="B20" t="n">
         <v>225.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
+      <c r="A21" t="n">
+        <v>1977</v>
       </c>
       <c r="B21" t="n">
         <v>205.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
+      <c r="A22" t="n">
+        <v>1978</v>
       </c>
       <c r="B22" t="n">
         <v>243.4</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1979</v>
       </c>
       <c r="B23" t="n">
         <v>237.1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1980</v>
       </c>
       <c r="B24" t="n">
         <v>226.8</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1981</v>
       </c>
       <c r="B25" t="n">
         <v>235.7</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1982</v>
       </c>
       <c r="B26" t="n">
         <v>234.2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1983</v>
       </c>
       <c r="B27" t="n">
         <v>230.3</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
+      <c r="A28" t="n">
+        <v>1984</v>
       </c>
       <c r="B28" t="n">
         <v>233.4</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
+      <c r="A29" t="n">
+        <v>1985</v>
       </c>
       <c r="B29" t="n">
         <v>225.9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
+      <c r="A30" t="n">
+        <v>1986</v>
       </c>
       <c r="B30" t="n">
         <v>240.3</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
+      <c r="A31" t="n">
+        <v>1987</v>
       </c>
       <c r="B31" t="n">
         <v>235.3</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
+      <c r="A32" t="n">
+        <v>1988</v>
       </c>
       <c r="B32" t="n">
         <v>225.3</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
+      <c r="A33" t="n">
+        <v>1989</v>
       </c>
       <c r="B33" t="n">
         <v>239.6</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
+      <c r="A34" t="n">
+        <v>1990</v>
       </c>
       <c r="B34" t="n">
         <v>248.9</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
+      <c r="A35" t="n">
+        <v>1991</v>
       </c>
       <c r="B35" t="n">
         <v>281.2</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B36" t="n">
+        <v>251.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>он</t>
         </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>үйлдвэрлэл_мянган_тонн</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1940</v>
+      </c>
+      <c r="B2" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B3" t="n">
+        <v>157.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B4" t="n">
+        <v>184.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>186.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="B6" t="n">
+        <v>168.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B7" t="n">
+        <v>146.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1964</v>
+      </c>
+      <c r="B8" t="n">
+        <v>141.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B9" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1966</v>
+      </c>
+      <c r="B10" t="n">
+        <v>171.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1967</v>
+      </c>
+      <c r="B11" t="n">
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B12" t="n">
+        <v>163.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B13" t="n">
+        <v>180.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B14" t="n">
+        <v>179.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B15" t="n">
+        <v>176.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B16" t="n">
+        <v>197.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B17" t="n">
+        <v>188.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B18" t="n">
+        <v>215.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1975</v>
+      </c>
+      <c r="B19" t="n">
+        <v>234.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1976</v>
+      </c>
+      <c r="B20" t="n">
+        <v>225.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B21" t="n">
+        <v>205.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1978</v>
+      </c>
+      <c r="B22" t="n">
+        <v>243.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1979</v>
+      </c>
+      <c r="B23" t="n">
+        <v>237.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B24" t="n">
+        <v>226.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B25" t="n">
+        <v>235.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B26" t="n">
+        <v>234.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B27" t="n">
+        <v>230.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1984</v>
+      </c>
+      <c r="B28" t="n">
+        <v>233.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1985</v>
+      </c>
+      <c r="B29" t="n">
+        <v>225.9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1986</v>
+      </c>
+      <c r="B30" t="n">
+        <v>240.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1987</v>
+      </c>
+      <c r="B31" t="n">
+        <v>235.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1988</v>
+      </c>
+      <c r="B32" t="n">
+        <v>225.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1989</v>
+      </c>
+      <c r="B33" t="n">
+        <v>239.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B34" t="n">
+        <v>248.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B35" t="n">
+        <v>281.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1992</v>
       </c>
       <c r="B36" t="n">
         <v>251.2</v>
